--- a/docs/02_機能毎のテスト/試験項目表_VLDT.xlsx
+++ b/docs/02_機能毎のテスト/試験項目表_VLDT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\#terasolunaorg\spring-functionaltest\docs\02_機能毎のテスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\git\spring-functionaltest\master\spring-functionaltest\docs\02_機能毎のテスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204432A8-3C9B-425D-AE39-4FF39B4F895A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E185EB91-4972-490A-86C4-063C35DB4F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大中項目" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="278">
   <si>
     <t>機能ID</t>
     <rPh sb="0" eb="2">
@@ -589,47 +589,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。</t>
-    <rPh sb="6" eb="7">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。</t>
-    <rPh sb="37" eb="39">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コレクション型でネスト対象のJavaBeanであること示すアノテーションを付与し、入力チェックエラーとなるリクエストをする。</t>
     <rPh sb="6" eb="7">
       <t>カタ</t>
@@ -645,55 +604,6 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1. 全フィールドに以下を指定する
-　SpringTest
-2. 全フィールドに何も設定せず、リクエストする</t>
-    <rPh sb="3" eb="4">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ゼン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>実施条件 1. 
-エラーメッセージが出力されていないこと
-実施条件 2. 
-以下のエラーメッセージフィールドの横に出力されること
-name       size must be between 1 and 50
-postcode size must be between 1 and 10
-address   size must be between 1 and 100</t>
-    <rPh sb="0" eb="2">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウケン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウケン</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>ヨコ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>シュツリョク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -721,36 +631,6 @@
     </rPh>
     <rPh sb="124" eb="126">
       <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1. AddressFormを使用する入力フィールドを2組作成し、全フィールドに以下を指定する
-　SpringTest
-2. 全フィールドに何も設定せず、リクエストする</t>
-    <rPh sb="15" eb="17">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>クミ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>ゼン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4635,6 +4515,345 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1. 全フィールドに何も設定せず、リクエストする</t>
+    <rPh sb="3" eb="4">
+      <t>ゼン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「No errors were found during input validation.」が表示されていること</t>
+    <rPh sb="48" eb="50">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全フィールドに以下を指定する
+　SpringTest</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。（入力チェックエラーがない場合）</t>
+    <rPh sb="37" eb="39">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。（入力チェックエラーがある場合）</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。（入力チェックエラーがある場合）</t>
+    <rPh sb="37" eb="39">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。（入力チェックエラーがない場合）</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AddressFormを使用する入力フィールドを2組作成し、全フィールドに以下を指定する
+　SpringTest</t>
+    <rPh sb="12" eb="14">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>クミ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。removeボタン押下で削除（サーサイドで実装）したAddressがvalidateボタン押下後も削除されていることを確認する。（入力チェックエラーがない場合）</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。removeボタン押下で削除（サーサイドで実装）したAddressがvalidateボタン押下後も削除されていることを確認する。（入力チェックエラーがある場合）</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。removeボタン押下で削除（JavaScriptで実装）したAddressがvalidateボタン押下後も削除されていることを確認する。（入力チェックエラーがない場合）</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コレクション型でネストしたJavaBeanにBeanValidationのアノテーションを付与した場合、ネスト先のフィールドも入力チェックできることを確認する。removeボタン押下で削除（JavaScriptで実装）したAddressがvalidateボタン押下後も削除されていることを確認する。（入力チェックエラーがある場合）</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1. Address 1の全フィールドに「名前1」「郵便番号1」「住所1」を入力する。
+2. addボタンを押下する。→Address 1（フィールドの値はそのまま）の下にAddress 2が追加されることを確認する。
+3. Address 2の全フィールドに「名前2」「郵便番号2」「住所2」を入力する。
+4. addボタンを押下する。→Address 2（フィールドの値はそのまま）の下にAddress 3が追加されることを確認する。
+5. Address 3の全フィールドに「名前3」「郵便番号3」「住所3」を入力する。
+6. Address 2のremoveボタンを押下する。→Address 2がなくなっていることとAddress 1/3のフィールドの値がそのままであることを確認する。
+7. validateボタンを押下する。</t>
+    <rPh sb="13" eb="14">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="292" eb="294">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="336" eb="337">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="348" eb="350">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="370" eb="372">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1. addボタンを押下する。→Address 1の下にAddress 2が追加されることを確認する。
+2. addボタンを押下する。→Address 2の下にAddress 3が追加されることを確認する。
+3. Address 2のremoveボタンを押下する。→Address 2がなくなっていることを確認する。
+4. validateボタンを押下する。</t>
+    <rPh sb="129" eb="131">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="155" eb="157">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1. Address 1の全フィールドに「名前1」「郵便番号1」「住所1」を入力する。
+2. addボタンを押下する。→Address 1（フィールドの値はそのまま）の下にAddress 2が追加されることを確認する。
+3. Address 2の各フィールドに「名前2」「郵便番号2」「住所2」を入力する。
+4. addボタンを押下する。→Address 2（各フィールドの値はそのまま）の下にAddress 3が追加されることを確認する。
+5. Address 3の各フィールドに「名前3」「郵便番号3」「住所3」を入力する。
+6. Address 2のremoveボタンを押下する。→Address 2がなくなっていることとAddress 1/3の各フィールドの値がそのままであることを確認する。
+7. validateボタンを押下する。</t>
+    <rPh sb="13" eb="14">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="125" eb="126">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="293" eb="295">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="338" eb="339">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="350" eb="352">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="372" eb="374">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>以下のエラーメッセージが各フィールドの下に出力されること
+UserName：size must be between 1 and 50
+PostCode：size must be between 1 and 10
+Address：size must be between 1 and 100</t>
+    <rPh sb="12" eb="13">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シュツリョク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -5606,15 +5825,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.26953125" customWidth="1"/>
-    <col min="3" max="3" width="13.6328125" customWidth="1"/>
+    <col min="1" max="1" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.20703125" customWidth="1"/>
+    <col min="3" max="3" width="13.62890625" customWidth="1"/>
     <col min="4" max="4" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5622,10 +5841,10 @@
         <v>24</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -5634,10 +5853,10 @@
       </c>
       <c r="C2" s="2" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">SUMPRODUCT(IF(LEFT($A$5:$A$65497, 4)=$B$1, N(INDIRECT($A$5:$A$65497 &amp; "!C2")), 0))</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -5651,7 +5870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="str">
         <f>IF(B5="","",($B$1&amp;TEXT(IF(B5="","",COUNTA($B$5:B5)),"00")))</f>
         <v>VLDT01</v>
@@ -5667,7 +5886,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="str">
         <f>IF(B6="","",($B$1&amp;TEXT(IF(B6="","",COUNTA($B$5:B6)),"00")))</f>
         <v/>
@@ -5681,7 +5900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="str">
         <f>IF(B7="","",($B$1&amp;TEXT(IF(B7="","",COUNTA($B$5:B7)),"00")))</f>
         <v/>
@@ -5695,7 +5914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="str">
         <f>IF(B8="","",($B$1&amp;TEXT(IF(B8="","",COUNTA($B$5:B8)),"00")))</f>
         <v/>
@@ -5706,10 +5925,10 @@
         <v>VLDT0104</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="str">
         <f>IF(B9="","",($B$1&amp;TEXT(IF(B9="","",COUNTA($B$5:B9)),"00")))</f>
         <v>VLDT02</v>
@@ -5722,10 +5941,10 @@
         <v>VLDT0201</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="str">
         <f>IF(B10="","",($B$1&amp;TEXT(IF(B10="","",COUNTA($B$5:B10)),"00")))</f>
         <v/>
@@ -5736,10 +5955,10 @@
         <v>VLDT0202</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="str">
         <f>IF(B11="","",($B$1&amp;TEXT(IF(B11="","",COUNTA($B$5:B11)),"00")))</f>
         <v>VLDT03</v>
@@ -5755,7 +5974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="str">
         <f>IF(B12="","",($B$1&amp;TEXT(IF(B12="","",COUNTA($B$5:B12)),"00")))</f>
         <v/>
@@ -5769,7 +5988,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="str">
         <f>IF(B13="","",($B$1&amp;TEXT(IF(B13="","",COUNTA($B$5:B13)),"00")))</f>
         <v/>
@@ -5780,10 +5999,10 @@
         <v>VLDT0303</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="38.700000000000003" x14ac:dyDescent="0.3">
       <c r="A14" s="38"/>
       <c r="B14" s="37"/>
       <c r="C14" s="20" t="str">
@@ -5791,10 +6010,10 @@
         <v>VLDT0304</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="38.700000000000003" x14ac:dyDescent="0.3">
       <c r="A15" s="38"/>
       <c r="B15" s="37"/>
       <c r="C15" s="20" t="str">
@@ -5802,10 +6021,10 @@
         <v>VLDT0305</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="str">
         <f>IF(B16="","",($B$1&amp;TEXT(IF(B16="","",COUNTA($B$5:B16)),"00")))</f>
         <v>VLDT04</v>
@@ -5821,7 +6040,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="str">
         <f>IF(B17="","",($B$1&amp;TEXT(IF(B17="","",COUNTA($B$5:B17)),"00")))</f>
         <v/>
@@ -5835,23 +6054,23 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="str">
         <f>IF(B18="","",($B$1&amp;TEXT(IF(B18="","",COUNTA($B$5:B18)),"00")))</f>
         <v>VLDT05</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C18" s="20" t="str">
         <f>IF(B18="",($B$1&amp;TEXT(IF(B18="",COUNTA($B$5:B18),1),"00")),A18)&amp;IF(B18&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A18&lt;&gt;"",1,RIGHT(C13,2)+1),"00"))</f>
         <v>VLDT0501</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38"/>
       <c r="B19" s="37"/>
       <c r="C19" s="20" t="str">
@@ -5859,26 +6078,26 @@
         <v>VLDT0502</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="str">
         <f>IF(B20="","",($B$1&amp;TEXT(IF(B20="","",COUNTA($B$5:B20)),"00")))</f>
         <v>VLDT06</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C20" s="20" t="str">
         <f>IF(B20="",($B$1&amp;TEXT(IF(B20="",COUNTA($B$5:B20),1),"00")),A20)&amp;IF(B20&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A20&lt;&gt;"",1,RIGHT(#REF!,2)+1),"00"))</f>
         <v>VLDT0601</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="str">
         <f>IF(B21="","",($B$1&amp;TEXT(IF(B21="","",COUNTA($B$5:B21)),"00")))</f>
         <v/>
@@ -5889,26 +6108,26 @@
         <v>VLDT0602</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="str">
         <f>IF(B22="","",($B$1&amp;TEXT(IF(B22="","",COUNTA($B$5:B22)),"00")))</f>
         <v>VLDT07</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C22" s="20" t="str">
         <f>IF(B22="",($B$1&amp;TEXT(IF(B22="",COUNTA($B$5:B22),1),"00")),A22)&amp;IF(B22&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A22&lt;&gt;"",1,RIGHT(C21,2)+1),"00"))</f>
         <v>VLDT0701</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="str">
         <f>IF(B23="","",($B$1&amp;TEXT(IF(B23="","",COUNTA($B$5:B23)),"00")))</f>
         <v/>
@@ -5919,22 +6138,22 @@
         <v>VLDT0702</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C24" s="20" t="str">
         <f>IF(B24="",($B$1&amp;TEXT(IF(B24="",COUNTA($B$5:B24),1),"00")),A24)&amp;IF(B24&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A24&lt;&gt;"",1,RIGHT(C21,2)+1),"00"))</f>
         <v>VLDT0801</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5960,20 +6179,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -5997,14 +6216,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="48">
-        <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
-        <v>20</v>
+        <f ca="1">COUNTIFS($B$9:$B$65501,"&lt;&gt;",$J$9:$J$65501,"&lt;&gt;論理削除")</f>
+        <v>26</v>
       </c>
       <c r="D2" s="18" t="str">
         <f>大中項目!B1</f>
@@ -6018,7 +6237,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -6034,7 +6253,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6045,7 +6264,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -6058,7 +6277,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -6071,7 +6290,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6082,7 +6301,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:12" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -6111,26 +6330,26 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="195" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f>大中項目!$C$5</f>
         <v>VLDT0101</v>
       </c>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B28" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
+        <f t="shared" ref="B9:B34" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>42</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>39</v>
@@ -6142,7 +6361,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -6152,25 +6371,25 @@
         <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="379.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="379.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15"/>
       <c r="B11" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -6180,25 +6399,25 @@
         <v>37</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="408.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -6208,25 +6427,25 @@
         <v>37</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="408.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
       <c r="B13" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -6236,25 +6455,25 @@
         <v>37</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="17">
         <f t="shared" ref="B14:B15" ca="1" si="1">IF(A14&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B14)-1,COLUMN(B14),4))+1)</f>
@@ -6264,26 +6483,26 @@
         <v>37</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="L14" s="22"/>
     </row>
-    <row r="15" spans="1:12" ht="117" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="116.1" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="17">
         <f t="shared" ca="1" si="1"/>
@@ -6293,26 +6512,26 @@
         <v>37</v>
       </c>
       <c r="D15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>107</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>112</v>
       </c>
       <c r="I15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="L15" s="22"/>
     </row>
-    <row r="16" spans="1:12" ht="117" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="116.1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="17">
         <f t="shared" ref="B16" ca="1" si="2">IF(A16&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B16)-1,COLUMN(B16),4))+1)</f>
@@ -6322,26 +6541,26 @@
         <v>37</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F16" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="H16" s="13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>38</v>
       </c>
       <c r="L16" s="22"/>
     </row>
-    <row r="17" spans="1:9" ht="130" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="129" x14ac:dyDescent="0.3">
       <c r="A17" s="15"/>
       <c r="B17" s="17">
         <f t="shared" ref="B17:B18" ca="1" si="3">IF(A17&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B17)-1,COLUMN(B17),4))+1)</f>
@@ -6351,25 +6570,25 @@
         <v>37</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E17" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="I17" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="286" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="283.8" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="17">
         <f t="shared" ca="1" si="3"/>
@@ -6379,25 +6598,25 @@
         <v>37</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="234" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="232.2" x14ac:dyDescent="0.3">
       <c r="A19" s="15"/>
       <c r="B19" s="17">
         <f ca="1">IF(A19&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B19)-1,COLUMN(B19),4))+1)</f>
@@ -6407,25 +6626,25 @@
         <v>37</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="234" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="232.2" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="17">
         <f t="shared" ref="B20" ca="1" si="4">IF(A20&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B20)-1,COLUMN(B20),4))+1)</f>
@@ -6435,25 +6654,25 @@
         <v>37</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="156" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="154.80000000000001" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
       <c r="B21" s="17">
         <f t="shared" ref="B21" ca="1" si="5">IF(A21&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B21)-1,COLUMN(B21),4))+1)</f>
@@ -6463,64 +6682,64 @@
         <v>37</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="104" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="103.2" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="17">
-        <f t="shared" ref="B22" ca="1" si="6">IF(A22&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B22)-1,COLUMN(B22),4))+1)</f>
+        <f t="shared" ref="B22:B23" ca="1" si="6">IF(A22&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B22)-1,COLUMN(B22),4))+1)</f>
         <v>14</v>
       </c>
       <c r="C22" s="35" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="210" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="str">
         <f>大中項目!$C$6</f>
         <v>VLDT0102</v>
       </c>
       <c r="B23" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>49</v>
+        <v>265</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>46</v>
@@ -6529,16 +6748,16 @@
         <v>47</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>52</v>
+        <v>263</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -6548,139 +6767,307 @@
         <v>37</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>48</v>
+        <v>267</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>52</v>
+        <v>277</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="353.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="str">
+    <row r="25" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="B25" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="B26" s="17">
+        <f t="shared" ref="B26:B28" ca="1" si="7">IF(A26&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B26)-1,COLUMN(B26),4))+1)</f>
+        <v>4</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="B27" s="17">
+        <f t="shared" ca="1" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="17">
+        <f t="shared" ca="1" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="B29" s="17">
+        <f t="shared" ref="B29" ca="1" si="8">IF(A29&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B29)-1,COLUMN(B29),4))+1)</f>
+        <v>7</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="B30" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="353.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="str">
         <f>大中項目!$C$7</f>
         <v>VLDT0103</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B31" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C31" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="D31" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="366.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="B32" s="17">
+        <f t="shared" ref="B32" ca="1" si="9">IF(A32&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B32)-1,COLUMN(B32),4))+1)</f>
+        <v>2</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="H32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I32" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="366.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="17">
-        <f t="shared" ref="B26" ca="1" si="7">IF(A26&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B26)-1,COLUMN(B26),4))+1)</f>
-        <v>2</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="236.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17">
+    <row r="33" spans="1:9" ht="236.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="B33" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C33" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="I27" s="14" t="s">
+      <c r="D33" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I33" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="315" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="str">
+    <row r="34" spans="1:9" ht="315" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="str">
         <f>大中項目!$C$8</f>
         <v>VLDT0104</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B34" s="19">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C34" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="I28" s="14" t="s">
+      <c r="D34" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I34" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6693,7 +7080,7 @@
     <mergeCell ref="A6:I6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A10:B28">
+  <conditionalFormatting sqref="A10:B34">
     <cfRule type="expression" dxfId="10" priority="1">
       <formula>A10&lt;&gt;""</formula>
     </cfRule>
@@ -6704,10 +7091,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I28" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I34" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Selenium:○,Seleniumu:△,Selenium:×,JUnit:○,JUnit:△,Junit:×,手動実行,机上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C28" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C34" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"正常,クライアントエラー,サーバーエラー"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6728,19 +7115,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -6764,7 +7151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -6785,7 +7172,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -6801,7 +7188,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6812,7 +7199,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -6825,7 +7212,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -6838,7 +7225,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6849,7 +7236,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -6878,7 +7265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="377" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="374.1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f>大中項目!$C$9</f>
         <v>VLDT0201</v>
@@ -6891,25 +7278,25 @@
         <v>37</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="408.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -6919,25 +7306,25 @@
         <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="408.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15"/>
       <c r="B11" s="17">
         <f t="shared" ref="B11" ca="1" si="1">IF(A11&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B11)-1,COLUMN(B11),4))+1)</f>
@@ -6947,25 +7334,25 @@
         <v>37</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="408.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="str">
         <f>大中項目!$C$10</f>
         <v>VLDT0202</v>
@@ -6978,25 +7365,25 @@
         <v>37</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="19">
         <f ca="1">IF(A13&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B13)-1,COLUMN(B13),4))+1)</f>
@@ -7006,19 +7393,19 @@
         <v>37</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>38</v>
@@ -7068,19 +7455,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -7104,7 +7491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -7125,7 +7512,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -7141,7 +7528,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7152,7 +7539,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -7165,7 +7552,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -7178,7 +7565,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -7189,7 +7576,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -7218,7 +7605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f>大中項目!$C$11</f>
         <v>VLDT0301</v>
@@ -7231,25 +7618,25 @@
         <v>37</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="str">
         <f>大中項目!$C$12</f>
         <v>VLDT0302</v>
@@ -7262,25 +7649,25 @@
         <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="338" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="335.4" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="str">
         <f>大中項目!$C$13</f>
         <v>VLDT0303</v>
@@ -7293,25 +7680,25 @@
         <v>37</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="str">
         <f>大中項目!$C$14</f>
         <v>VLDT0304</v>
@@ -7324,25 +7711,25 @@
         <v>37</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="str">
         <f>大中項目!$C$15</f>
         <v>VLDT0305</v>
@@ -7354,19 +7741,19 @@
         <v>37</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>38</v>
@@ -7416,19 +7803,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -7452,7 +7839,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -7473,7 +7860,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -7489,7 +7876,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7500,7 +7887,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -7513,7 +7900,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -7526,7 +7913,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -7537,7 +7924,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -7566,7 +7953,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="403" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="399.9" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f>大中項目!$C$16</f>
         <v>VLDT0401</v>
@@ -7579,25 +7966,25 @@
         <v>37</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="str">
         <f>大中項目!$C$17</f>
         <v>VLDT0402</v>
@@ -7610,25 +7997,25 @@
         <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="19">
         <f t="shared" ca="1" si="0"/>
@@ -7638,19 +8025,19 @@
         <v>37</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>38</v>
@@ -7695,19 +8082,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -7731,7 +8118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -7752,7 +8139,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -7768,7 +8155,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7779,7 +8166,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -7792,7 +8179,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -7805,7 +8192,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -7816,7 +8203,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -7845,7 +8232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="104" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="103.2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="str">
         <f>大中項目!$C$18</f>
         <v>VLDT0501</v>
@@ -7858,27 +8245,27 @@
         <v>37</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="104" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="103.2" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B10" s="19">
         <f t="shared" ca="1" si="0"/>
@@ -7888,19 +8275,19 @@
         <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
@@ -7945,19 +8332,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -7981,7 +8368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -8002,7 +8389,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -8018,7 +8405,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -8029,7 +8416,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -8042,7 +8429,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -8055,7 +8442,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -8066,7 +8453,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>4</v>
       </c>
@@ -8095,7 +8482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="247" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="245.1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f>大中項目!$C$20</f>
         <v>VLDT0601</v>
@@ -8105,112 +8492,112 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="247" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="245.1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="24">
         <f t="shared" ref="B10:B22" ca="1" si="1">IF(A10&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B10)-1,COLUMN(B10),4))+1)</f>
         <v>2</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>127</v>
-      </c>
       <c r="H10" s="13" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="247" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="245.1" x14ac:dyDescent="0.3">
       <c r="A11" s="15"/>
       <c r="B11" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E11" s="13" t="s">
+      <c r="H11" s="13" t="s">
         <v>124</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="247" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="245.1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E12" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>124</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="266.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="266.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="60" t="str">
         <f>大中項目!$C$21</f>
         <v>VLDT0602</v>
@@ -8220,28 +8607,28 @@
         <v>1</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G13" s="56" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H13" s="56" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I13" s="58" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="394.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="394.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="61"/>
       <c r="B14" s="63"/>
       <c r="C14" s="65"/>
@@ -8252,225 +8639,225 @@
       <c r="H14" s="57"/>
       <c r="I14" s="59"/>
     </row>
-    <row r="15" spans="1:9" ht="65" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="64.5" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="24">
         <f ca="1">IF(A15&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B15)-2,COLUMN(B15),4))+1)</f>
         <v>2</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I15" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="78" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="64.5" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="78" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="77.400000000000006" x14ac:dyDescent="0.3">
       <c r="A17" s="15"/>
       <c r="B17" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>140</v>
-      </c>
       <c r="H17" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="65" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="64.5" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="65" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="64.5" x14ac:dyDescent="0.3">
       <c r="A19" s="15"/>
       <c r="B19" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="104" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="90.3" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="104" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="90.3" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
       <c r="B21" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>8</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="104" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="90.3" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>9</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E22" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>144</v>
-      </c>
       <c r="H22" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>38</v>
@@ -8521,19 +8908,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -8557,7 +8944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -8578,7 +8965,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -8594,7 +8981,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -8605,7 +8992,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -8618,7 +9005,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -8631,7 +9018,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -8642,7 +9029,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>4</v>
       </c>
@@ -8671,7 +9058,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="247" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="245.1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f>大中項目!$C$22</f>
         <v>VLDT0701</v>
@@ -8681,28 +9068,28 @@
         <v>1</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="247" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="245.1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="24">
         <f t="shared" ca="1" si="0"/>
@@ -8712,25 +9099,25 @@
         <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="221" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="219.3" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="str">
         <f>大中項目!$C$23</f>
         <v>VLDT0702</v>
@@ -8740,28 +9127,28 @@
         <v>1</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I11" s="29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="221" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="219.3" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="24">
         <f t="shared" ca="1" si="0"/>
@@ -8771,19 +9158,19 @@
         <v>37</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>38</v>
@@ -8824,19 +9211,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" customWidth="1"/>
-    <col min="6" max="7" width="41.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.20703125" customWidth="1"/>
+    <col min="2" max="2" width="8.62890625" customWidth="1"/>
+    <col min="3" max="3" width="10.3671875" customWidth="1"/>
+    <col min="4" max="4" width="25.1015625" customWidth="1"/>
+    <col min="5" max="5" width="42.68359375" customWidth="1"/>
+    <col min="6" max="7" width="41.68359375" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
@@ -8860,7 +9247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
@@ -8881,7 +9268,7 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="47"/>
       <c r="C3" s="49"/>
@@ -8897,7 +9284,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -8908,7 +9295,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
@@ -8921,7 +9308,7 @@
       <c r="H5" s="51"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>14</v>
       </c>
@@ -8934,7 +9321,7 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -8945,7 +9332,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>4</v>
       </c>
@@ -8974,7 +9361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="str">
         <f>大中項目!$C$24</f>
         <v>VLDT0801</v>
@@ -8984,22 +9371,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>38</v>
